--- a/docs/The_Called_Client_Tracker.xlsx
+++ b/docs/The_Called_Client_Tracker.xlsx
@@ -47,7 +47,7 @@
     <font>
       <name val="Arial"/>
       <i val="1"/>
-      <color rgb="006B7280"/>
+      <color rgb="006E6A62"/>
       <sz val="10"/>
     </font>
     <font>
@@ -62,7 +62,7 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="006B4EFF"/>
+      <color rgb="003A3833"/>
       <sz val="10"/>
     </font>
     <font>
@@ -78,29 +78,29 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="006B7280"/>
+      <color rgb="006E6A62"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <i val="1"/>
-      <color rgb="006B7280"/>
+      <color rgb="006E6A62"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="006B4EFF"/>
+      <color rgb="003A3833"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="006B4EFF"/>
+      <color rgb="003A3833"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="006B7280"/>
+      <color rgb="006E6A62"/>
       <sz val="9"/>
     </font>
     <font>
@@ -109,7 +109,7 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="006B7280"/>
+      <color rgb="006E6A62"/>
       <sz val="8"/>
     </font>
     <font>
@@ -121,7 +121,7 @@
     <font>
       <name val="Arial"/>
       <i val="1"/>
-      <color rgb="006B7280"/>
+      <color rgb="006E6A62"/>
       <sz val="8"/>
     </font>
     <font>
@@ -139,32 +139,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00111318"/>
+        <fgColor rgb="001B1916"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EFEAFF"/>
+        <fgColor rgb="00E1DFDB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E6F4EA"/>
+        <fgColor rgb="00E7F0E5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF8DC"/>
+        <fgColor rgb="00FCF3E3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F1F3F5"/>
+        <fgColor rgb="00F2F1EF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="006B4EFF"/>
+        <fgColor rgb="003A3833"/>
       </patternFill>
     </fill>
   </fills>
@@ -178,30 +178,30 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D7DAE0"/>
+        <color rgb="00D6D3CC"/>
       </left>
       <right style="thin">
-        <color rgb="00D7DAE0"/>
+        <color rgb="00D6D3CC"/>
       </right>
       <top style="thin">
-        <color rgb="00D7DAE0"/>
+        <color rgb="00D6D3CC"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D7DAE0"/>
+        <color rgb="00D6D3CC"/>
       </bottom>
     </border>
     <border>
       <left style="medium">
-        <color rgb="006B4EFF"/>
+        <color rgb="003A3833"/>
       </left>
       <right style="medium">
-        <color rgb="006B4EFF"/>
+        <color rgb="003A3833"/>
       </right>
       <top style="medium">
-        <color rgb="006B4EFF"/>
+        <color rgb="003A3833"/>
       </top>
       <bottom style="medium">
-        <color rgb="006B4EFF"/>
+        <color rgb="003A3833"/>
       </bottom>
     </border>
   </borders>
@@ -363,14 +363,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="00E6F4EA"/>
+          <bgColor rgb="00E7F0E5"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="00FCE8E6"/>
+          <bgColor rgb="00F7E4E0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -378,11 +378,11 @@
       <font>
         <name val="Arial"/>
         <b val="1"/>
-        <color rgb="00137333"/>
+        <color rgb="002F6B3A"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="00E6F4EA"/>
+          <bgColor rgb="00E7F0E5"/>
         </patternFill>
       </fill>
     </dxf>
@@ -390,22 +390,22 @@
       <font>
         <name val="Arial"/>
         <b val="1"/>
-        <color rgb="00C5221F"/>
+        <color rgb="00A83A2C"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="00FCE8E6"/>
+          <bgColor rgb="00F7E4E0"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
         <name val="Arial"/>
-        <color rgb="00C5221F"/>
+        <color rgb="00A83A2C"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="00FCE8E6"/>
+          <bgColor rgb="00F7E4E0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1589,7 +1589,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00111318"/>
+    <tabColor rgb="001B1916"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1984,7 +1984,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="006B4EFF"/>
+    <tabColor rgb="008E8A82"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -2209,7 +2209,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="006B4EFF"/>
+    <tabColor rgb="008E8A82"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -13751,7 +13751,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00111318"/>
+    <tabColor rgb="001B1916"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -14747,7 +14747,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="006B4EFF"/>
+    <tabColor rgb="008E8A82"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -16995,7 +16995,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00111318"/>
+    <tabColor rgb="001B1916"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
